--- a/dataset/3_tax_and_charges_rules/structured/Fyers_brokerage_and_fees_by_date.xlsx
+++ b/dataset/3_tax_and_charges_rules/structured/Fyers_brokerage_and_fees_by_date.xlsx
@@ -19,19 +19,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
-  </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -47,7 +36,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -55,31 +44,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -378,55 +348,116 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>from</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>to</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>verified_on</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>confidence</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2">
-        <v>40269</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2010-04-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2020-03-31</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>S11 We don't levy any charges to open an account with us (support article archived 2020-01-02)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>assumed</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>No account-opening fee appears on any archived Fyers page from 2015-11 to 2020, and S11 (archived 2020-01-02) says none is charged. Fyers did not operate before 2015, so nil is a stand-in for the years before.</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2">
-        <v>43922</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2020-04-01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2020-11-23</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>S11 With effect from 1st April 2020, the online/offline account opening fees of Rs 400 + GST</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2">
-        <v>44159</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2020-11-24</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -438,8 +469,10 @@
           <t>S11 With effect from 24th November 2020, the account opening charges are Nil</t>
         </is>
       </c>
-      <c r="E4" s="2">
-        <v>46294</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -463,42 +496,42 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>cohort</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>from</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>to</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>verified_on</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>confidence</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -510,6 +543,41 @@
           <t>legacy</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2010-04-01</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2019-11-14</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>S7 Demat Annual Maintenance Charges levied by IL&amp;FS (ISSL): Rs 400 + Tax</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>assumed</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Seen on Fyers pages from 2018-09-15 to 2019-09-23 and assumed for earlier years. Levied by the ISSL demat participant. ISSL holders may have paid it until their migration in January 2021; not modelled.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -517,6 +585,36 @@
           <t>legacy</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2019-11-15</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>S8 Demat Annual Maintenance Charges: FREE; S10 accounts opened on or before 31st March 2020 continue with zero AMC</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Date is the first archived copy showing Fyers' own demat with no AMC (2019-11-15).</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -524,6 +622,41 @@
           <t>standard</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2020-04-01</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2021-09-30</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>S10 With effect from 1st April 2020, the Demat AMC of Rs 300 + GST will be levied per annum</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Accounts opened from 2020-12-01 pay Rs 225 in their first year (first quarter waived); not modelled, so this can overcharge Rs 75 + GST once.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -531,6 +664,31 @@
           <t>standard</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2021-10-01</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>S16 Demat Annual Maintenance Charges (AMC) are waived off for all our existing customers with effect from 1st October 2021</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -538,8 +696,10 @@
           <t>free</t>
         </is>
       </c>
-      <c r="B6" s="2">
-        <v>44402</v>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2021-07-25</t>
+        </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -551,8 +711,10 @@
           <t>S12 Demat AMC: FREE; S16 Free AMC offer extended indefinitely; S1 today: Rs 0</t>
         </is>
       </c>
-      <c r="F6" s="2">
-        <v>46294</v>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -576,55 +738,116 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>from</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>to</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>cohort</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>verified_on</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>confidence</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2">
-        <v>40269</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2010-04-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2020-03-31</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>legacy</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>S10 all clients who have opened their Demat accounts with us on or before 31st March 2020 will be continued with zero AMC</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2">
-        <v>43922</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2020-04-01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2021-07-24</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>S10 With effect from 1st April 2020, the Demat AMC of Rs 300 + GST will be levied per annum</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Start date is stated by Fyers. End date is inferred: the free-AMC offer for new clients is first seen on the archived pricing page of 2021-07-25; the copy of 2021-05-16 does not show it.</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2">
-        <v>44402</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2021-07-25</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -636,8 +859,10 @@
           <t>S12 Demat AMC: FREE (Limited Period Offer Valid Till 31/7/2021); S16 free AMC offer extended indefinitely</t>
         </is>
       </c>
-      <c r="E4" s="2">
-        <v>46294</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -661,52 +886,52 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>product</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>from</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>to</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>mode</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>verified_on</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>confidence</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>flat</t>
         </is>
@@ -718,6 +943,46 @@
           <t>delivery</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2010-04-01</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2015-11-13</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.001</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>S3 Equity Delivery: 0.1% of Turnover on each leg</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>assumed</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Fyers was not yet operating (its earliest archived price page is 2015-11-14 and its CEO says it started in 2015). The earliest known schedule is used as a stand-in.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -725,6 +990,46 @@
           <t>delivery</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2015-11-14</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2016-04-12</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.001</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>S3 Equity Delivery: 0.1% of Turnover on each leg</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>First archived copy of the schedule is 2015-11-14; it may have started earlier. Last archived copy with this schedule: 2016-03-16.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -732,6 +1037,51 @@
           <t>delivery</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2016-04-13</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2017-08-07</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>min_flat_pct</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0.001</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>S4 Equity Delivery: 0.1% or Rs 100 per order (whichever is lower)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Date inferred from archived copies: last copy with the old schedule 2016-03-16; first copy with the new one 2016-04-13. from = first copy.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -739,6 +1089,51 @@
           <t>delivery</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2017-08-08</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2018-02-05</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>min_flat_pct</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0.001</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>S5 Equity Delivery: Rs 20 per executed order or 0.1% (whichever is lower)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Date inferred from archived copies: last copy with the old schedule 2016-04-14; first copy with the new one 2017-08-08. from = first copy.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -746,6 +1141,41 @@
           <t>delivery</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2018-02-06</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>zero</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>S6 With effect from 6th February 2018, we have introduced Zero Brokerage for equity delivery segment</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Zero brokerage on delivery. Fyers pages up to 2024-09 still list zero delivery brokerage.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -753,6 +1183,46 @@
           <t>delivery</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>min_flat_pct</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0.003</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>S14 Equity Delivery: Revised to 0.3% or Rs 20 per executed order, whichever is lower (effective October 1, 2024)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Same on today's Standard plan (S1, S2): Rs 20 or 0.3% for Delivery, ETF and MTF.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -760,6 +1230,46 @@
           <t>futures</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2010-04-01</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2015-11-13</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0.0001</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>S3 Equity Futures: 0.01% of Turnover on each leg</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>assumed</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Fyers was not yet operating (its earliest archived price page is 2015-11-14 and its CEO says it started in 2015). The earliest known schedule is used as a stand-in.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -767,6 +1277,46 @@
           <t>futures</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2015-11-14</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2016-04-12</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0.0001</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>S3 Equity Futures: 0.01% of Turnover on each leg</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>First archived copy of the schedule is 2015-11-14; it may have started earlier. Last archived copy with this schedule: 2016-03-16.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -774,6 +1324,51 @@
           <t>futures</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2016-04-13</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2017-08-07</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>min_flat_pct</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0.0001</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>S4 Equity Futures: 0.01% or Rs 100 per order (whichever is lower)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Date inferred from archived copies: last copy with the old schedule 2016-03-16; first copy with the new one 2016-04-13. from = first copy.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -781,6 +1376,51 @@
           <t>futures</t>
         </is>
       </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2017-08-08</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2020-05-10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>min_flat_pct</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0.0001</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>S5 Futures: Rs 20 per executed order or 0.01% (whichever is lower)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Date inferred from archived copies: last copy with the old schedule 2016-04-14; first copy with the new one 2017-08-08. from = first copy.</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -788,8 +1428,10 @@
           <t>futures</t>
         </is>
       </c>
-      <c r="B12" s="2">
-        <v>43962</v>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2020-05-11</t>
+        </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -806,8 +1448,10 @@
           <t>S9 Instead of 0.01%, it will be 0.03% or Rs 20 (whichever is lower) for futures ... with effect from 11th May 2020</t>
         </is>
       </c>
-      <c r="G12" s="2">
-        <v>46294</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -836,75 +1480,262 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>from</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>to</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>basis</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>verified_on</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>confidence</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2">
-        <v>40269</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2010-04-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2018-09-14</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>per_sale</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>S7 Demat Debit Transaction charges levied by IL&amp;FS (ISSL): Rs 20 + Depository charges at actuals</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>assumed</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>No demat charges were published on any archived Fyers page before 2018-09-15; the earliest known value is used as a stand-in.</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2">
-        <v>43358</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2018-09-15</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2019-11-14</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>per_sale</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>S7 Demat Debit Transaction charges levied by IL&amp;FS (ISSL): Rs 20 + Depository charges at actuals</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Levied by the ISSL demat participant. First archived copy 2018-09-15; last copy with it 2019-09-23; Fyers' own demat starts with the copy of 2019-11-15.</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2">
-        <v>43784</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2019-11-15</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2021-08-12</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>per_sale</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>S8 Debit Charges (Sell): Rs 10 + Rs 5.50 (CDSL Charges); S17 confirms</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Fyers' own part is Rs 10. Date is the first archived copy showing it (2019-11-15); last ISSL-era copy 2019-09-23.</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2">
-        <v>44421</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2021-08-13</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>per_sale</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>S12 Demat Debit Charges: Rs 7 + Rs 5.5 (CDSL Charges); S13 same on 2024-07-19</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Fyers' own part is Rs 7 (total Rs 12.5, the figure S14 calls the pre-October-2024 charge). Date is the first archived copy showing it; last copy with Rs 10 is 2021-07-25.</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2">
-        <v>45566</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>per_sale</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>S14 The DP charges will be reduced from Rs 12.5 per transaction to Rs 3.5 per transaction (effective October 1, 2024)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Fyers' own part is zero; the Rs 3.5 that remains is the CDSL fee (Fyers charges list of 2024-11-13: Rs 3.5 (CDSL Charges) per transaction).</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2">
-        <v>45810</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -921,8 +1752,10 @@
           <t>S15 a single, flat charge of Rs 12.5 + GST per stock (ISIN) per day, from 2nd June 2025; S1 splits it as Rs 3.5 CDSL + Rs 9 Fyers</t>
         </is>
       </c>
-      <c r="F7" s="2">
-        <v>46294</v>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
